--- a/InputData/elec/TCCpUCD/Trans Const Cost per Unit Cap Dist.xlsx
+++ b/InputData/elec/TCCpUCD/Trans Const Cost per Unit Cap Dist.xlsx
@@ -1,27 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\TCCpUCD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-southkorea\InputData\elec\TCCpUCD\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3325FEA3-F413-4A4D-BC54-CE03D437BF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="195" yWindow="98" windowWidth="17220" windowHeight="8205"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="TCCpUCD" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>TCCpUCD Transmission Construction Cost per Unit Capacity Distance</t>
   </si>
@@ -29,83 +41,47 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>National Renewable Energy Laboratory</t>
-  </si>
-  <si>
-    <t>Renewable Energy Futures Study: Volume 1</t>
-  </si>
-  <si>
-    <t>http://www.nrel.gov/docs/fy12osti/52409-1.pdf</t>
-  </si>
-  <si>
-    <t>Page 3-14, Figure 3-8</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Additional MW-miles</t>
+    <t>Transmission Construction</t>
+  </si>
+  <si>
+    <t>Note:</t>
+  </si>
+  <si>
+    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
+  </si>
+  <si>
+    <t>Cost per Unit Capacity Distance (2012$/(circuit mile))</t>
   </si>
   <si>
     <t>MW-miles</t>
   </si>
   <si>
-    <t>Annual cost (2010-2050)</t>
-  </si>
-  <si>
-    <t>Total cost</t>
-  </si>
-  <si>
-    <t>Cost per MW-mile</t>
-  </si>
-  <si>
-    <t>We assume that the currency figures in RE Futures are in real dollars</t>
-  </si>
-  <si>
-    <t>and the annual cost from 2010-2050 refers to a period of 40 years,</t>
-  </si>
-  <si>
-    <t>not 41 years (e.g. going from the end of 2010 to the end of 2050).</t>
-  </si>
-  <si>
-    <t>(value read from graph)</t>
-  </si>
-  <si>
-    <t>Transmission Construction</t>
-  </si>
-  <si>
-    <t>Note:</t>
-  </si>
-  <si>
-    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
-  </si>
-  <si>
-    <t>We assume NREL's 2010-2050 figures are in real 2010 dollars.</t>
-  </si>
-  <si>
-    <t>We adjust 2010 dollars to 2012 dollars using the following conversion factor:</t>
-  </si>
-  <si>
-    <t>2010 $</t>
-  </si>
-  <si>
-    <t>2012 $</t>
-  </si>
-  <si>
-    <t>Cost per Unit Capacity Distance (2012$/(MW*mile))</t>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>$ / MW-mile</t>
+  </si>
+  <si>
+    <t>Americans for a Clean Energy Grid and Grid Strategies</t>
+  </si>
+  <si>
+    <t>Transmission Projects Ready To Go: Plugging Into America's Untapped Renewable Resources</t>
+  </si>
+  <si>
+    <t>https://cleanenergygrid.org/wp-content/uploads/2019/04/Transmission-Projects-Ready-to-Go-Final.pdf</t>
+  </si>
+  <si>
+    <t>Pages 11-12</t>
+  </si>
+  <si>
+    <t>We adjust 2021 dollars to 2012 dollars using the following conversion factor:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,14 +101,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -161,24 +129,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -229,55 +185,43 @@
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="8">
-    <cellStyle name="Body: normal cell" xfId="5"/>
-    <cellStyle name="Font: Calibri, 9pt regular" xfId="3"/>
-    <cellStyle name="Footnotes: top row" xfId="7"/>
-    <cellStyle name="Header: bottom row" xfId="4"/>
+    <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Font: Calibri, 9pt regular" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Footnotes: top row" xfId="7" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Header: bottom row" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Parent row" xfId="6"/>
-    <cellStyle name="Table title" xfId="2"/>
+    <cellStyle name="Parent row" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Table title" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -368,6 +312,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -403,6 +364,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -578,176 +556,64 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="44.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>0.84730412960844359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" s="12">
-        <v>1.0549999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="25.19921875" customWidth="1"/>
-    <col min="2" max="2" width="11.53125" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="5">
-        <f>122*10^6</f>
-        <v>122000000</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="5">
-        <f>6.5*10^9</f>
-        <v>6500000000</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <f>B7*(2050-2010)</f>
-        <v>260000000000</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="14">
-        <f>B8/B6</f>
-        <v>2131.1475409836066</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="10">
-        <f>B9*About!$A$12</f>
-        <v>2248.3606557377047</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -755,30 +621,72 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1">
+        <f>17*10^6</f>
+        <v>17000000</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <f>33*10^9</f>
+        <v>33000000000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <f>A2/A1</f>
+        <v>1941.1764705882354</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.86328125" customWidth="1"/>
-    <col min="2" max="2" width="11.86328125" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B2" s="6">
-        <f>Data!B10</f>
-        <v>2248.3606557377047</v>
+        <f>Data!A3*About!A11</f>
+        <v>1644.7668398281553</v>
       </c>
     </row>
   </sheetData>
@@ -787,31 +695,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -819,24 +728,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -855,70 +825,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1029,23 +952,10 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AB2DABE-1D38-455D-AD13-05B34CC5BFF7}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{300A1BA1-7A44-4A68-BCE6-F677E6F8C09E}"/>
-</file>
-
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B7DE4C7-A79D-4C22-8262-B320D82CC226}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9675A698-FC6C-4864-917C-3B0A3B2D63D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCADEE96-F48F-4DA6-A9E7-8EFC1E8A525A}"/>
 </file>